--- a/code/data/combined/cmb+dmul-w0wacdm-fixed.xlsx
+++ b/code/data/combined/cmb+dmul-w0wacdm-fixed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39213913.99865019</v>
+        <v>44425444.09451787</v>
       </c>
       <c r="C2" t="n">
-        <v>-134286934.5338362</v>
+        <v>-148685611.4127091</v>
       </c>
       <c r="D2" t="n">
-        <v>40645477.10146383</v>
+        <v>46689835.98824252</v>
       </c>
       <c r="E2" t="n">
-        <v>-410392.9037214859</v>
+        <v>-468237.0928358654</v>
       </c>
       <c r="F2" t="n">
-        <v>-1418702.450870231</v>
+        <v>-1421460.028101909</v>
       </c>
       <c r="G2" t="n">
-        <v>882064.6769150585</v>
+        <v>1050448.297683481</v>
       </c>
       <c r="H2" t="n">
-        <v>6341212.528218763</v>
+        <v>7261795.865528615</v>
       </c>
       <c r="I2" t="n">
-        <v>1714925.701638476</v>
+        <v>1964134.81533676</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134286934.5262697</v>
+        <v>-148685611.4169711</v>
       </c>
       <c r="C3" t="n">
-        <v>887991069.0679032</v>
+        <v>895782919.218704</v>
       </c>
       <c r="D3" t="n">
-        <v>-89476835.97214971</v>
+        <v>-111911248.995336</v>
       </c>
       <c r="E3" t="n">
-        <v>15741702.57373893</v>
+        <v>16344774.50299212</v>
       </c>
       <c r="F3" t="n">
-        <v>6695175.623908853</v>
+        <v>6648185.514545184</v>
       </c>
       <c r="G3" t="n">
-        <v>-3840600.547502949</v>
+        <v>-4444658.21621001</v>
       </c>
       <c r="H3" t="n">
-        <v>-24772829.79804783</v>
+        <v>-27644008.25808717</v>
       </c>
       <c r="I3" t="n">
-        <v>-6679845.540715151</v>
+        <v>-7459016.137654018</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40645477.1022861</v>
+        <v>46689835.98794728</v>
       </c>
       <c r="C4" t="n">
-        <v>-89476835.98316266</v>
+        <v>-111911248.9896514</v>
       </c>
       <c r="D4" t="n">
-        <v>49444924.02883179</v>
+        <v>55547151.11228671</v>
       </c>
       <c r="E4" t="n">
-        <v>942916.4143614132</v>
+        <v>855710.4824678353</v>
       </c>
       <c r="F4" t="n">
-        <v>-1134934.082289926</v>
+        <v>-1159056.221570592</v>
       </c>
       <c r="G4" t="n">
-        <v>966618.6948836596</v>
+        <v>1147987.178527142</v>
       </c>
       <c r="H4" t="n">
-        <v>6579923.332362041</v>
+        <v>7621302.075355472</v>
       </c>
       <c r="I4" t="n">
-        <v>1782597.820568882</v>
+        <v>2064243.872981746</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-410392.9034471507</v>
+        <v>-468237.0930477517</v>
       </c>
       <c r="C5" t="n">
-        <v>15741702.5729752</v>
+        <v>16344774.50358539</v>
       </c>
       <c r="D5" t="n">
-        <v>942916.4146768849</v>
+        <v>855710.4822258448</v>
       </c>
       <c r="E5" t="n">
-        <v>982978.4599322762</v>
+        <v>1070203.214642436</v>
       </c>
       <c r="F5" t="n">
-        <v>24342.18684460564</v>
+        <v>43220.67306774357</v>
       </c>
       <c r="G5" t="n">
-        <v>-74077.02686330558</v>
+        <v>-81632.91825598909</v>
       </c>
       <c r="H5" t="n">
-        <v>-264044.086103762</v>
+        <v>-294441.0110390651</v>
       </c>
       <c r="I5" t="n">
-        <v>-70664.21381123678</v>
+        <v>-78921.85736406222</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1418702.450859576</v>
+        <v>-1421460.027887591</v>
       </c>
       <c r="C6" t="n">
-        <v>6695175.623967191</v>
+        <v>6648185.513819012</v>
       </c>
       <c r="D6" t="n">
-        <v>-1134934.082267342</v>
+        <v>-1159056.221338447</v>
       </c>
       <c r="E6" t="n">
-        <v>24342.18684749795</v>
+        <v>43220.67306282197</v>
       </c>
       <c r="F6" t="n">
-        <v>747842.7102508277</v>
+        <v>748820.2786754429</v>
       </c>
       <c r="G6" t="n">
-        <v>107300.5174998464</v>
+        <v>106083.3443321114</v>
       </c>
       <c r="H6" t="n">
-        <v>-32207.17347139975</v>
+        <v>-36088.89667455242</v>
       </c>
       <c r="I6" t="n">
-        <v>-11083.48393439403</v>
+        <v>-12122.33601683522</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>882064.6768870574</v>
+        <v>1050448.297763841</v>
       </c>
       <c r="C7" t="n">
-        <v>-3840600.547649907</v>
+        <v>-4444658.216328703</v>
       </c>
       <c r="D7" t="n">
-        <v>966618.6948271416</v>
+        <v>1147987.178625394</v>
       </c>
       <c r="E7" t="n">
-        <v>-74077.02687149975</v>
+        <v>-81632.91825036313</v>
       </c>
       <c r="F7" t="n">
-        <v>107300.5174997535</v>
+        <v>106083.3443248051</v>
       </c>
       <c r="G7" t="n">
-        <v>66677.42738634124</v>
+        <v>72577.55396868046</v>
       </c>
       <c r="H7" t="n">
-        <v>227892.1413586983</v>
+        <v>259238.0130212366</v>
       </c>
       <c r="I7" t="n">
-        <v>62139.79157404749</v>
+        <v>70629.44695627688</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6341212.528137513</v>
+        <v>7261795.865684465</v>
       </c>
       <c r="C8" t="n">
-        <v>-24772829.79913748</v>
+        <v>-27644008.25781851</v>
       </c>
       <c r="D8" t="n">
-        <v>6579923.332125615</v>
+        <v>7621302.0755809</v>
       </c>
       <c r="E8" t="n">
-        <v>-264044.086151357</v>
+        <v>-294441.0110034281</v>
       </c>
       <c r="F8" t="n">
-        <v>-32207.17347254876</v>
+        <v>-36088.89671360311</v>
       </c>
       <c r="G8" t="n">
-        <v>227892.1413611174</v>
+        <v>259238.0130119149</v>
       </c>
       <c r="H8" t="n">
-        <v>1200137.243700064</v>
+        <v>1368239.033353583</v>
       </c>
       <c r="I8" t="n">
-        <v>325354.9730231737</v>
+        <v>370869.5218554987</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1714925.701616232</v>
+        <v>1964134.815380256</v>
       </c>
       <c r="C9" t="n">
-        <v>-6679845.541008337</v>
+        <v>-7459016.137585459</v>
       </c>
       <c r="D9" t="n">
-        <v>1782597.820504742</v>
+        <v>2064243.873044223</v>
       </c>
       <c r="E9" t="n">
-        <v>-70664.21382410238</v>
+        <v>-78921.85735444217</v>
       </c>
       <c r="F9" t="n">
-        <v>-11083.48393470295</v>
+        <v>-12122.33602741471</v>
       </c>
       <c r="G9" t="n">
-        <v>62139.79157469343</v>
+        <v>70629.44695379578</v>
       </c>
       <c r="H9" t="n">
-        <v>325354.9730231268</v>
+        <v>370869.5218557343</v>
       </c>
       <c r="I9" t="n">
-        <v>88478.61545572497</v>
+        <v>100802.0124121292</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+dmul-w0wacdm-fixed.xlsx
+++ b/code/data/combined/cmb+dmul-w0wacdm-fixed.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44425444.09451787</v>
+        <v>43575294.86995421</v>
       </c>
       <c r="C2" t="n">
-        <v>-148685611.4127091</v>
+        <v>-145846347.9607224</v>
       </c>
       <c r="D2" t="n">
-        <v>46689835.98824252</v>
+        <v>45770888.48987613</v>
       </c>
       <c r="E2" t="n">
-        <v>-468237.0928358654</v>
+        <v>-460982.2864744269</v>
       </c>
       <c r="F2" t="n">
-        <v>-1421460.028101909</v>
+        <v>-1413843.634672101</v>
       </c>
       <c r="G2" t="n">
-        <v>1050448.297683481</v>
+        <v>1023557.719137686</v>
       </c>
       <c r="H2" t="n">
-        <v>7261795.865528615</v>
+        <v>7110737.359735454</v>
       </c>
       <c r="I2" t="n">
-        <v>1964134.81533676</v>
+        <v>1923225.024996133</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148685611.4169711</v>
+        <v>-145846347.9585333</v>
       </c>
       <c r="C3" t="n">
-        <v>895782919.218704</v>
+        <v>876933849.2812426</v>
       </c>
       <c r="D3" t="n">
-        <v>-111911248.995336</v>
+        <v>-110082289.1000173</v>
       </c>
       <c r="E3" t="n">
-        <v>16344774.50299212</v>
+        <v>16113321.63928958</v>
       </c>
       <c r="F3" t="n">
-        <v>6648185.514545184</v>
+        <v>6575874.493966163</v>
       </c>
       <c r="G3" t="n">
-        <v>-4444658.21621001</v>
+        <v>-4351201.156873096</v>
       </c>
       <c r="H3" t="n">
-        <v>-27644008.25808717</v>
+        <v>-27114073.03970904</v>
       </c>
       <c r="I3" t="n">
-        <v>-7459016.137654018</v>
+        <v>-7315638.476925557</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46689835.98794728</v>
+        <v>45770888.49004002</v>
       </c>
       <c r="C4" t="n">
-        <v>-111911248.9896514</v>
+        <v>-110082289.1031138</v>
       </c>
       <c r="D4" t="n">
-        <v>55547151.11228671</v>
+        <v>54387207.01724891</v>
       </c>
       <c r="E4" t="n">
-        <v>855710.4824678353</v>
+        <v>837194.9051036135</v>
       </c>
       <c r="F4" t="n">
-        <v>-1159056.221570592</v>
+        <v>-1155120.540945282</v>
       </c>
       <c r="G4" t="n">
-        <v>1147987.178527142</v>
+        <v>1119448.477098668</v>
       </c>
       <c r="H4" t="n">
-        <v>7621302.075355472</v>
+        <v>7461160.879001314</v>
       </c>
       <c r="I4" t="n">
-        <v>2064243.872981746</v>
+        <v>2020852.795597164</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-468237.0930477517</v>
+        <v>-460982.2863970624</v>
       </c>
       <c r="C5" t="n">
-        <v>16344774.50358539</v>
+        <v>16113321.63914171</v>
       </c>
       <c r="D5" t="n">
-        <v>855710.4822258448</v>
+        <v>837194.9052047472</v>
       </c>
       <c r="E5" t="n">
-        <v>1070203.214642436</v>
+        <v>1062321.036120527</v>
       </c>
       <c r="F5" t="n">
-        <v>43220.67306774357</v>
+        <v>43141.09560146807</v>
       </c>
       <c r="G5" t="n">
-        <v>-81632.91825598909</v>
+        <v>-81084.23474662322</v>
       </c>
       <c r="H5" t="n">
-        <v>-294441.0110390651</v>
+        <v>-292019.9768548404</v>
       </c>
       <c r="I5" t="n">
-        <v>-78921.85736406222</v>
+        <v>-78273.66679834831</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1421460.027887591</v>
+        <v>-1413843.634729333</v>
       </c>
       <c r="C6" t="n">
-        <v>6648185.513819012</v>
+        <v>6575874.494033359</v>
       </c>
       <c r="D6" t="n">
-        <v>-1159056.221338447</v>
+        <v>-1155120.541020679</v>
       </c>
       <c r="E6" t="n">
-        <v>43220.67306282197</v>
+        <v>43141.09559751727</v>
       </c>
       <c r="F6" t="n">
-        <v>748820.2786754429</v>
+        <v>744664.3838505889</v>
       </c>
       <c r="G6" t="n">
-        <v>106083.3443321114</v>
+        <v>105952.213942087</v>
       </c>
       <c r="H6" t="n">
-        <v>-36088.89667455242</v>
+        <v>-35039.19184816297</v>
       </c>
       <c r="I6" t="n">
-        <v>-12122.33601683522</v>
+        <v>-11831.17049107153</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1050448.297763841</v>
+        <v>1023557.719108152</v>
       </c>
       <c r="C7" t="n">
-        <v>-4444658.216328703</v>
+        <v>-4351201.156892228</v>
       </c>
       <c r="D7" t="n">
-        <v>1147987.178625394</v>
+        <v>1119448.477055657</v>
       </c>
       <c r="E7" t="n">
-        <v>-81632.91825036313</v>
+        <v>-81084.2347501247</v>
       </c>
       <c r="F7" t="n">
-        <v>106083.3443248051</v>
+        <v>105952.2139434887</v>
       </c>
       <c r="G7" t="n">
-        <v>72577.55396868046</v>
+        <v>71670.12460156243</v>
       </c>
       <c r="H7" t="n">
-        <v>259238.0130212366</v>
+        <v>254362.8095352364</v>
       </c>
       <c r="I7" t="n">
-        <v>70629.44695627688</v>
+        <v>69310.0098775861</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7261795.865684465</v>
+        <v>7110737.359673588</v>
       </c>
       <c r="C8" t="n">
-        <v>-27644008.25781851</v>
+        <v>-27114073.03998248</v>
       </c>
       <c r="D8" t="n">
-        <v>7621302.0755809</v>
+        <v>7461160.878893432</v>
       </c>
       <c r="E8" t="n">
-        <v>-294441.0110034281</v>
+        <v>-292019.9768701033</v>
       </c>
       <c r="F8" t="n">
-        <v>-36088.89671360311</v>
+        <v>-35039.19183927496</v>
       </c>
       <c r="G8" t="n">
-        <v>259238.0130119149</v>
+        <v>254362.8095383254</v>
       </c>
       <c r="H8" t="n">
-        <v>1368239.033353583</v>
+        <v>1341152.501803717</v>
       </c>
       <c r="I8" t="n">
-        <v>370869.5218554987</v>
+        <v>363535.3612964941</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1964134.815380256</v>
+        <v>1923225.024978839</v>
       </c>
       <c r="C9" t="n">
-        <v>-7459016.137585459</v>
+        <v>-7315638.476998057</v>
       </c>
       <c r="D9" t="n">
-        <v>2064243.873044223</v>
+        <v>2020852.795567368</v>
       </c>
       <c r="E9" t="n">
-        <v>-78921.85735444217</v>
+        <v>-78273.66680251058</v>
       </c>
       <c r="F9" t="n">
-        <v>-12122.33602741471</v>
+        <v>-11831.17048866595</v>
       </c>
       <c r="G9" t="n">
-        <v>70629.44695379578</v>
+        <v>69310.00987840829</v>
       </c>
       <c r="H9" t="n">
-        <v>370869.5218557343</v>
+        <v>363535.3612964086</v>
       </c>
       <c r="I9" t="n">
-        <v>100802.0124121292</v>
+        <v>98816.13673013037</v>
       </c>
     </row>
   </sheetData>
